--- a/data/trans_camb/P32-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,05</t>
+          <t>0,45; 6,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,46</t>
+          <t>-0,38; 5,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,45</t>
+          <t>1,36; 9,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,81</t>
+          <t>-4,31; 1,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,82</t>
+          <t>-4,8; 1,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,83</t>
+          <t>-4,36; 1,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,18</t>
+          <t>-0,27; 4,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,91</t>
+          <t>-0,65; 3,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,96</t>
+          <t>1,05; 7,29</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 328,26</t>
+          <t>4,26; 319,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 289,43</t>
+          <t>-15,2; 296,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,59; 442,84</t>
+          <t>22,54; 440,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 257,58</t>
+          <t>-13,24; 226,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 209,02</t>
+          <t>-21,95; 218,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 380,85</t>
+          <t>16,8; 393,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,28</t>
+          <t>2,53; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,86</t>
+          <t>0,61; 3,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,32</t>
+          <t>1,16; 5,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,35</t>
+          <t>-1,09; 2,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,7</t>
+          <t>0,23; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,08</t>
+          <t>-1,69; 2,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,47</t>
+          <t>1,78; 4,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,47</t>
+          <t>0,94; 3,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,28</t>
+          <t>0,02; 3,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,44; 289,88</t>
+          <t>68,6; 286,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,49; 184,5</t>
+          <t>13,28; 183,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,24; 234,25</t>
+          <t>33,75; 249,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 224,88</t>
+          <t>-44,58; 301,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 407,81</t>
+          <t>3,69; 444,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,16; 204,24</t>
+          <t>-62,08; 186,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,27; 221,6</t>
+          <t>57,52; 233,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 178,64</t>
+          <t>30,23; 176,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 159,39</t>
+          <t>2,15; 162,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,5</t>
+          <t>0,63; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,15</t>
+          <t>0,73; 7,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,36</t>
+          <t>1,09; 7,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,02</t>
+          <t>-0,01; 5,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,17</t>
+          <t>0,62; 5,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,25</t>
+          <t>1,03; 6,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,48</t>
+          <t>0,86; 5,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,45</t>
+          <t>1,04; 5,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,11</t>
+          <t>1,46; 5,78</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 711,4</t>
+          <t>7,73; 833,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 679,06</t>
+          <t>-5,17; 632,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 600,86</t>
+          <t>9,99; 694,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 647,36</t>
+          <t>20,18; 617,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,27; 634,35</t>
+          <t>29,03; 652,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,34; 814,16</t>
+          <t>39,26; 726,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,4</t>
+          <t>2,63; 5,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,92</t>
+          <t>1,26; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,16</t>
+          <t>2,11; 5,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,99</t>
+          <t>-0,66; 1,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,07</t>
+          <t>0,43; 3,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,27</t>
+          <t>-0,73; 2,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,92</t>
+          <t>1,88; 4,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,19</t>
+          <t>1,27; 3,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,54</t>
+          <t>0,93; 3,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,14; 244,51</t>
+          <t>74,52; 245,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,59; 179,37</t>
+          <t>36,61; 165,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58,03; 224,36</t>
+          <t>62,52; 230,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 213,3</t>
+          <t>-36,52; 204,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,06; 355,76</t>
+          <t>11,73; 362,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 217,01</t>
+          <t>-34,63; 258,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,56; 201,94</t>
+          <t>65,76; 203,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,85; 160,87</t>
+          <t>43,21; 164,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,17; 174,27</t>
+          <t>35,88; 177,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,18</t>
+          <t>0,37; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,4</t>
+          <t>-0,46; 5,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,07</t>
+          <t>1,72; 9,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,79</t>
+          <t>-4,43; 1,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,48</t>
+          <t>-4,8; 1,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,96</t>
+          <t>-4,75; 1,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,02</t>
+          <t>-0,01; 4,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,9</t>
+          <t>-0,64; 3,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,29</t>
+          <t>1,15; 7,05</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160,64%</t>
+          <t>172,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-31,79%</t>
+          <t>-36,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136,93%</t>
+          <t>144,15%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 319,36</t>
+          <t>2,59; 351,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 296,84</t>
+          <t>-17,22; 308,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,54; 440,33</t>
+          <t>35,13; 497,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 226,29</t>
+          <t>-8,16; 230,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 218,13</t>
+          <t>-24,5; 212,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,8; 393,74</t>
+          <t>19,68; 367,21</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>2,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,2</t>
+          <t>2,55; 6,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,95</t>
+          <t>0,58; 3,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,45</t>
+          <t>1,45; 5,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,42</t>
+          <t>-0,91; 2,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,94</t>
+          <t>0,01; 3,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,18</t>
+          <t>-0,15; 3,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,51</t>
+          <t>1,9; 4,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,37</t>
+          <t>0,93; 3,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,29</t>
+          <t>1,23; 4,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104,99%</t>
+          <t>115,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>109,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,6; 286,07</t>
+          <t>67,85; 304,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 183,5</t>
+          <t>15,03; 184,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,75; 249,4</t>
+          <t>39,73; 248,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 301,85</t>
+          <t>-41,82; 235,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 444,64</t>
+          <t>-3,34; 417,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 186,53</t>
+          <t>-17,72; 368,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,52; 233,57</t>
+          <t>62,77; 238,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,23; 176,03</t>
+          <t>29,89; 181,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 162,79</t>
+          <t>41,7; 218,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,82</t>
+          <t>0,47; 7,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,0</t>
+          <t>0,59; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,49</t>
+          <t>1,48; 7,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,55</t>
+          <t>-0,08; 5,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,8</t>
+          <t>0,94; 6,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,76</t>
+          <t>1,33; 7,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,52</t>
+          <t>0,69; 5,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,36</t>
+          <t>1,27; 5,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,78</t>
+          <t>1,99; 6,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192,59%</t>
+          <t>208,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>597,84%</t>
+          <t>715,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>230,18%</t>
+          <t>257,9%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,73; 833,97</t>
+          <t>-7,69; 665,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 632,25</t>
+          <t>4,05; 598,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 694,63</t>
+          <t>24,64; 720,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,18; 617,56</t>
+          <t>16,45; 577,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,03; 652,64</t>
+          <t>40,87; 690,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,26; 726,84</t>
+          <t>61,08; 899,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>3,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,45</t>
+          <t>2,7; 5,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,76</t>
+          <t>1,2; 3,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,18</t>
+          <t>2,37; 5,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,92</t>
+          <t>-0,57; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,13</t>
+          <t>0,5; 3,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,41</t>
+          <t>0,81; 3,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,01</t>
+          <t>1,89; 3,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,19</t>
+          <t>1,14; 3,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,59</t>
+          <t>2,05; 4,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126,96%</t>
+          <t>138,51%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>133,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101,95%</t>
+          <t>133,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,52; 245,04</t>
+          <t>78,28; 254,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,61; 165,91</t>
+          <t>34,91; 180,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62,52; 230,4</t>
+          <t>71,42; 255,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 204,3</t>
+          <t>-29,65; 231,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,73; 362,33</t>
+          <t>22,61; 353,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 258,27</t>
+          <t>29,76; 413,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,76; 203,62</t>
+          <t>66,54; 204,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,21; 164,98</t>
+          <t>40,66; 173,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,88; 177,24</t>
+          <t>73,32; 227,01</t>
         </is>
       </c>
     </row>
